--- a/KatalonData/EmailTextToPay/Manage_EmailText_2.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_2.xlsx
@@ -8,20 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{20EE2F28-74A7-472F-8E31-23E91F1031C0}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{C878CE42-9DBC-4D13-AA42-9A332631ABCA}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="7" firstSheet="7" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView activeTab="17" firstSheet="16" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="ManageEmailTextSearch" r:id="rId1" sheetId="1"/>
     <sheet name="ManageEmailTextFilter_FirstName" r:id="rId2" sheetId="2"/>
     <sheet name="ManageEmailTextFilter_LastName" r:id="rId3" sheetId="6"/>
     <sheet name="ManageEmailTextFilter_CompName" r:id="rId4" sheetId="7"/>
-    <sheet name="ManageEmailTextResend" r:id="rId5" sheetId="3"/>
-    <sheet name="ManageEmailTextExpire" r:id="rId6" sheetId="4"/>
-    <sheet name="ManageEmailTextCopy" r:id="rId7" sheetId="5"/>
-    <sheet name="ManageEmailText_Errors_Search" r:id="rId8" sheetId="8"/>
-    <sheet name="ManageEmailText_Errors_NoSearch" r:id="rId9" sheetId="9"/>
+    <sheet name="ManageEmailTextResend_FirstName" r:id="rId5" sheetId="3"/>
+    <sheet name="ManageEmailTextResend_LastName" r:id="rId6" sheetId="10"/>
+    <sheet name="ManageEmailTextResend_CompName" r:id="rId7" sheetId="11"/>
+    <sheet name="ManageEmailTextExpire_CompName" r:id="rId8" sheetId="13"/>
+    <sheet name="ManageEmailTextExpire_FirstName" r:id="rId9" sheetId="4"/>
+    <sheet name="ManageEmailTextExpire_LastName" r:id="rId10" sheetId="12"/>
+    <sheet name="ManageEmailTextCopy_FirstName" r:id="rId11" sheetId="5"/>
+    <sheet name="ManageEmailTextCopy_LastName" r:id="rId12" sheetId="14"/>
+    <sheet name="ManageEmailTextCopy_CompName" r:id="rId13" sheetId="15"/>
+    <sheet name="ManageEmailText_Errors_Search" r:id="rId14" sheetId="8"/>
+    <sheet name="ManageEmailText_Errors_NoSearch" r:id="rId15" sheetId="9"/>
+    <sheet name="ManageEmailTxtFilter_Par1stName" r:id="rId16" sheetId="16"/>
+    <sheet name="ManageEmailTxtFilter_ParLastNam" r:id="rId17" sheetId="17"/>
+    <sheet name="ManageEmailTxtFilter_ParCompNam" r:id="rId18" sheetId="18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="88">
   <si>
     <t>Result</t>
   </si>
@@ -83,9 +92,6 @@
 Status-&gt; Active, Action-&gt; Expire &amp; Resend</t>
   </si>
   <si>
-    <t>Mon Apr 06 22:53:58 IST 2026</t>
-  </si>
-  <si>
     <t>Search + verify success message</t>
   </si>
   <si>
@@ -97,14 +103,8 @@
 verifying- Recipient/Company Name+Status+Action. </t>
   </si>
   <si>
-    <t>Tue Apr 07 19:44:08 IST 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search+ Filter for Company Name + verify success message +
 verifying- Recipient/Company Name+Status+Action. </t>
-  </si>
-  <si>
-    <t>Tue Apr 07 19:52:15 IST 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Search+ Filter for First Name + Action as 'Resend' :
@@ -114,9 +114,6 @@
 Verify-Recipient/Company Name+Status + Action. </t>
   </si>
   <si>
-    <t>Tue Apr 07 20:36:47 IST 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search+ Filter for Last Name + Action as 'Expire' :
 Click Expire button.
 Verify Pop up.
@@ -128,9 +125,6 @@
   </si>
   <si>
     <t>Wed Apr 08 16:56:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Apr 08 17:10:29 IST 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Search+ Filter for Company Name + Action as 'Copy' :
@@ -308,10 +302,97 @@
     <t>Thu Apr 09 20:54:50 IST 2026</t>
   </si>
   <si>
+    <t>Thu Apr 09 21:28:36 IST 2026</t>
+  </si>
+  <si>
+    <t>ZVJpVUcDCX aMEeGTjClw</t>
+  </si>
+  <si>
+    <t>FirstName &amp; LastName:
+Payment Application is selected.
+Click Search.
+Apply Filter with FirstName &amp; LastName</t>
+  </si>
+  <si>
+    <t>FirstName &amp; CompanyName:
+Payment Application is selected.
+Click Search.
+Apply Filter with FirstName &amp; CompanyName</t>
+  </si>
+  <si>
+    <t>LastName &amp; CompanyName:
+Payment Application is selected.
+Click Search.
+Apply Filter with LastName &amp; CompanyName</t>
+  </si>
+  <si>
+    <t>ZVJpVUcDCX RrQiAvzHyA</t>
+  </si>
+  <si>
+    <t>aMEeGTjClw RrQiAvzHyA</t>
+  </si>
+  <si>
+    <t>Mon Apr 13 16:15:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 13 16:16:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 13 16:17:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 13 17:18:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 13 17:20:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 14 18:07:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 14 18:18:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 14 18:22:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 14 19:01:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 14 19:06:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 15 19:20:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 15 19:31:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 15 19:36:43 IST 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search+ Filter for Partial First Name + verify success message +
+verifying- Recipient/Company Name+Status+Action. </t>
+  </si>
+  <si>
+    <t>Mon Apr 20 19:29:16 IST 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search+ Filter for Partial Last Name + verify success message +
+verifying- Recipient/Company Name+Status+Action. </t>
+  </si>
+  <si>
+    <t>Mon Apr 20 19:37:25 IST 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search+ Filter for Partial company Name + verify success message +
+verifying- Recipient/Company Name+Status+Action. </t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Thu Apr 09 21:28:36 IST 2026</t>
+    <t>Mon Apr 20 19:43:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -406,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
@@ -458,6 +539,9 @@
     </xf>
     <xf applyAlignment="1" applyFill="1" borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,10 +910,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -874,6 +958,922 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB20ABE5-EB40-4301-BBE4-8B897354D04D}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="46.1796875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="37.81640625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03671AC8-56DE-457F-802A-D25D162F1818}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="49.1796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="19.7265625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8D7B23-96A3-4C14-84F1-69CBEB776D28}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="49.1796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="19.7265625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEFB455-878E-4283-8CDF-5280F5D2D976}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="49.1796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="19.7265625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7F82F-C603-4F07-8548-EF17D188B148}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="48.36328125" collapsed="true"/>
+    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="24.81640625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="49.0" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="51.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="18.5" r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C3" s="4"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="13" r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="4"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row ht="75" r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>59686725</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="62.5" r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="75" r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="75" r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="62.5" r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="62.5" r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="62.5" r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E26A7E4-F23A-4B0C-8BC6-AFD45C94E0CE}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="48.36328125" collapsed="true"/>
+    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="13.90625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="49.0" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row ht="62.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row ht="13" r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row ht="62.5" r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row ht="62.5" r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" s="4"/>
+    </row>
+    <row customHeight="1" ht="55" r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="55" r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="55" r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row ht="13" r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" s="4"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row ht="50" r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row ht="13" r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="4"/>
+      <c r="E13" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B68FE70-BD03-498B-B600-6B4B7C132BA1}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="17" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="17" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="15" width="51.08984375" collapsed="true"/>
+    <col min="4" max="4" style="17" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="17" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="17" width="47.0" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="17" width="10.7265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="17" width="10.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="17" width="16.453125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="17" width="12.0" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="17" width="16.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="17" width="13.26953125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="17" width="13.453125" collapsed="true"/>
+    <col min="14" max="15" style="17" width="8.7265625" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="17" width="13.90625" collapsed="true"/>
+    <col min="17" max="20" style="17" width="8.7265625" collapsed="true"/>
+    <col min="21" max="21" customWidth="true" style="17" width="5.6328125" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="17" width="6.26953125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="17" width="6.0" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="17" width="5.90625" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="17" width="5.6328125" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="17" width="6.54296875" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="15" width="47.08984375" collapsed="true"/>
+    <col min="28" max="16384" style="17" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="38" r="2" s="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EABB53-51F5-4A90-B8E2-ADBC54583C91}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="17" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="17" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="15" width="51.08984375" collapsed="true"/>
+    <col min="4" max="4" style="17" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="17" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="17" width="47.0" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="17" width="10.7265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="17" width="10.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="17" width="16.453125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="17" width="12.0" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="17" width="16.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="17" width="13.26953125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="17" width="13.453125" collapsed="true"/>
+    <col min="14" max="15" style="17" width="8.7265625" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="17" width="13.90625" collapsed="true"/>
+    <col min="17" max="20" style="17" width="8.7265625" collapsed="true"/>
+    <col min="21" max="21" customWidth="true" style="17" width="5.6328125" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="17" width="6.26953125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="17" width="6.0" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="17" width="5.90625" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="17" width="5.6328125" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="17" width="6.54296875" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="15" width="47.08984375" collapsed="true"/>
+    <col min="28" max="16384" style="17" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="38" r="2" s="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD67883-E46D-4766-8983-E96E92BD2427}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="17" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="17" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="15" width="51.08984375" collapsed="true"/>
+    <col min="4" max="4" style="17" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="17" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="17" width="47.0" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="17" width="10.7265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="17" width="10.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="17" width="16.453125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="17" width="12.0" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="17" width="16.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="17" width="13.26953125" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="17" width="13.453125" collapsed="true"/>
+    <col min="14" max="15" style="17" width="8.7265625" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="17" width="13.90625" collapsed="true"/>
+    <col min="17" max="20" style="17" width="8.7265625" collapsed="true"/>
+    <col min="21" max="21" customWidth="true" style="17" width="5.6328125" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="17" width="6.26953125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="17" width="6.0" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="17" width="5.90625" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="17" width="5.6328125" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="17" width="6.54296875" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="15" width="47.08984375" collapsed="true"/>
+    <col min="28" max="16384" style="17" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="38" r="2" s="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -933,10 +1933,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1010,10 +2010,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1087,10 +2087,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1144,10 +2144,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1178,6 +2178,203 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D613A990-B35A-40B9-8717-E014B2376EAA}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="46.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="47.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C48FAA-06E6-4269-9430-6E787AF33FF2}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="16.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="46.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="47.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" customHeight="1" ht="78" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row customFormat="1" customHeight="1" ht="19" r="3" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B02ABF-6BE7-42F8-924B-66A45432828E}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="15.81640625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="46.1796875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="37.81640625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row customFormat="1" ht="75" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CBCA1D-16A9-43B0-BA4E-60CC8E0C88C7}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -1213,10 +2410,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1227,472 +2424,6 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03671AC8-56DE-457F-802A-D25D162F1818}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" customWidth="true" width="15.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" width="49.1796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="19.7265625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="38.0" collapsed="true"/>
-  </cols>
-  <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC7F82F-C603-4F07-8548-EF17D188B148}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="48.36328125" collapsed="true"/>
-    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.90625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="13.90625" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="49.0" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="8.7265625" collapsed="true"/>
-  </cols>
-  <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="51.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="18.5" r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="4"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row ht="13" r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C5" s="4"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row ht="75" r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="6">
-        <v>59686725</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row ht="62.5" r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row ht="75" r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row ht="75" r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E26A7E4-F23A-4B0C-8BC6-AFD45C94E0CE}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="1" width="8.7265625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="48.36328125" collapsed="true"/>
-    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.90625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="13.90625" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="49.0" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="8.7265625" collapsed="true"/>
-  </cols>
-  <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row ht="62.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row ht="13" r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row ht="62.5" r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row ht="62.5" r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row ht="62.5" r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C7" s="4"/>
-    </row>
-    <row customHeight="1" ht="55" r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="55" r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="55" r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row ht="13" r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="4"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row ht="50" r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="G12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row ht="13" r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="4"/>
-      <c r="E13" s="5"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/KatalonData/EmailTextToPay/Manage_EmailText_2.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_2.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="132">
   <si>
     <t>Result</t>
   </si>
@@ -393,6 +393,138 @@
   </si>
   <si>
     <t>Mon Apr 20 19:43:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:57:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:58:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:59:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:00:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:00:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:02:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:03:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:03:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:04:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:05:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:05:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:06:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:06:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:07:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:08:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:08:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:09:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:10:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:10:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:11:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:12:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:13:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:14:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:15:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:16:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:17:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:17:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:18:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:20:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:22:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:23:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 15:24:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:28:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:29:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:29:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:31:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:32:38 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -910,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>12</v>
@@ -997,7 +1129,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -1053,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
@@ -1109,7 +1241,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
@@ -1165,7 +1297,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
@@ -1350,7 +1482,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>63</v>
@@ -1373,7 +1505,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>64</v>
@@ -1396,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>65</v>
@@ -1462,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>42</v>
@@ -1488,7 +1620,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>45</v>
@@ -1508,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>46</v>
@@ -1528,7 +1660,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>47</v>
@@ -1551,7 +1683,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>26</v>
@@ -1574,7 +1706,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>27</v>
@@ -1597,7 +1729,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>28</v>
@@ -1624,7 +1756,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>44</v>
@@ -1702,7 +1834,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>81</v>
@@ -1779,7 +1911,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>83</v>
@@ -1856,7 +1988,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>85</v>
@@ -1933,7 +2065,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>13</v>
@@ -2010,7 +2142,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>14</v>
@@ -2087,7 +2219,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>15</v>
@@ -2144,7 +2276,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -2213,7 +2345,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -2282,7 +2414,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -2354,7 +2486,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -2410,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>

--- a/KatalonData/EmailTextToPay/Manage_EmailText_2.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{C878CE42-9DBC-4D13-AA42-9A332631ABCA}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{D494D00A-527F-4EB0-B18E-2834CE58E109}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="17" firstSheet="16" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView activeTab="16" firstSheet="15" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="ManageEmailTextSearch" r:id="rId1" sheetId="1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="104">
   <si>
     <t>Result</t>
   </si>
@@ -119,12 +119,6 @@
 Verify Pop up.
 Verify success message.
 Verify-Recipient/Company Name+Status + Action. </t>
-  </si>
-  <si>
-    <t>Tue Apr 07 21:53:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Apr 08 16:56:05 IST 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Search+ Filter for Company Name + Action as 'Copy' :
@@ -278,33 +272,6 @@
     <t>Thu Apr 09 20:15:58 IST 2026</t>
   </si>
   <si>
-    <t>Thu Apr 09 20:37:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:40:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:41:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:42:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:42:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:43:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:43:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 20:54:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 09 21:28:36 IST 2026</t>
-  </si>
-  <si>
     <t>ZVJpVUcDCX aMEeGTjClw</t>
   </si>
   <si>
@@ -332,199 +299,156 @@
     <t>aMEeGTjClw RrQiAvzHyA</t>
   </si>
   <si>
-    <t>Mon Apr 13 16:15:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Apr 13 16:16:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Apr 13 16:17:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Apr 13 17:18:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Apr 13 17:20:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 14 18:07:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 14 18:18:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 14 18:22:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 14 19:01:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 14 19:06:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Apr 15 19:20:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Apr 15 19:31:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Apr 15 19:36:43 IST 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search+ Filter for Partial First Name + verify success message +
 verifying- Recipient/Company Name+Status+Action. </t>
   </si>
   <si>
-    <t>Mon Apr 20 19:29:16 IST 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search+ Filter for Partial Last Name + verify success message +
 verifying- Recipient/Company Name+Status+Action. </t>
   </si>
   <si>
-    <t>Mon Apr 20 19:37:25 IST 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search+ Filter for Partial company Name + verify success message +
 verifying- Recipient/Company Name+Status+Action. </t>
   </si>
   <si>
+    <t>Thu Apr 30 18:28:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:29:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:29:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:31:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 18:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:12:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:14:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:20:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:23:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:26:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:28:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:31:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:33:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:35:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:38:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:41:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue May 12 15:22:38 IST 2026</t>
+  </si>
+  <si>
+    <t>2026-05-13 12:58:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search+ Filter for Last Name + Action as 'Resend' :
+Click Resend button.
+Verify Pop up.
+Verify success message.
+Verify-Recipient/Company Name+Status + Action. </t>
+  </si>
+  <si>
+    <t>Wed May 13 14:02:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 14:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search+ Filter for Company Name + Action as 'Resend' :
+Click Resend button.
+Verify Pop up.
+Verify success message.
+Verify-Recipient/Company Name+Status + Action. </t>
+  </si>
+  <si>
+    <t>Wed May 13 14:22:56 IST 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Mon Apr 20 19:43:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:57:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:58:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:59:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:00:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:00:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:02:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:03:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:03:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:04:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:05:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:05:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:06:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:06:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:07:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:08:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:08:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:09:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:09:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:10:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:10:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:11:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:12:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:13:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:14:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:15:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:16:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:17:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:17:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:18:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:19:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:20:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:21:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:22:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:23:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 15:24:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:28:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:29:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:29:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:30:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:30:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:31:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:32:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 18:32:38 IST 2026</t>
+    <t>Wed May 13 14:31:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 14:39:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 14:46:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 15:00:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 15:09:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 15:23:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 18:20:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 18:27:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 18:34:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 18:40:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 18:55:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 19:01:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 13 19:22:04 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1009,12 +933,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
     <col min="2" max="2" customWidth="true" style="9" width="15.36328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="4" width="34.54296875" collapsed="true"/>
     <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
     <col min="5" max="5" customWidth="true" style="1" width="13.54296875" collapsed="true"/>
     <col min="6" max="16384" style="1" width="8.7265625" collapsed="true"/>
@@ -1042,7 +966,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>12</v>
@@ -1054,16 +978,15 @@
         <v>5</v>
       </c>
     </row>
-    <row customHeight="1" ht="21.5" r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="B3"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row customHeight="1" ht="38" r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
     </row>
-    <row customHeight="1" ht="38" r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
     </row>
@@ -1082,10 +1005,6 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="B9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10"/>
-      <c r="B10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1129,7 +1048,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -1182,13 +1101,13 @@
     </row>
     <row customFormat="1" ht="150" r="2" s="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1241,10 +1160,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1297,10 +1216,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1349,10 +1268,10 @@
         <v>7</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row customHeight="1" ht="51.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1360,13 +1279,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row customHeight="1" ht="18.5" r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1378,19 +1300,22 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="13" r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1402,10 +1327,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>5</v>
@@ -1414,7 +1342,7 @@
         <v>59686725</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="62.5" r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1422,19 +1350,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="75" r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1442,19 +1373,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="75" r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1462,19 +1396,22 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="62.5" r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1482,10 +1419,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
@@ -1494,10 +1431,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="62.5" r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1505,10 +1442,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
@@ -1517,10 +1454,10 @@
         <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row ht="62.5" r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1528,10 +1465,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -1540,10 +1477,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1583,10 +1520,10 @@
         <v>7</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row ht="62.5" r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1594,10 +1531,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1607,7 +1544,7 @@
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="13" r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1620,19 +1557,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="62.5" r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1640,19 +1577,19 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="62.5" r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1660,19 +1597,19 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1683,10 +1620,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
@@ -1695,10 +1632,10 @@
         <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row customHeight="1" ht="55" r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1706,10 +1643,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -1718,10 +1655,10 @@
         <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row customHeight="1" ht="55" r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1729,10 +1666,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
@@ -1741,10 +1678,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="13" r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1756,17 +1693,17 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="5"/>
       <c r="G12" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="13" r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1834,10 +1771,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1911,10 +1848,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1988,10 +1925,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -2065,7 +2002,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>13</v>
@@ -2142,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>14</v>
@@ -2219,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>15</v>
@@ -2276,7 +2213,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -2345,10 +2282,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -2414,10 +2351,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -2486,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -2542,7 +2479,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
